--- a/OMOP Analysis/Results/Overall/overall_combined_bootstrap_summary_encounters_OMOP.xlsx
+++ b/OMOP Analysis/Results/Overall/overall_combined_bootstrap_summary_encounters_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -418,7 +418,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>38.317</v>
+        <v>38.312</v>
       </c>
       <c r="C2">
         <v>0.061</v>
@@ -430,133 +430,59 @@
         <v>0.008</v>
       </c>
       <c r="F2">
-        <v>37.827</v>
+        <v>37.823</v>
       </c>
       <c r="G2">
-        <v>38.796</v>
+        <v>38.792</v>
       </c>
       <c r="H2">
-        <v>37.802</v>
+        <v>37.797</v>
       </c>
       <c r="I2">
-        <v>38.782</v>
+        <v>38.778</v>
       </c>
       <c r="J2">
-        <v>37.846</v>
+        <v>37.841</v>
       </c>
       <c r="K2">
-        <v>38.827</v>
+        <v>38.822</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B3">
-        <v>22.659</v>
+        <v>39.25</v>
       </c>
       <c r="C3">
-        <v>0.026</v>
+        <v>0.065</v>
       </c>
       <c r="D3">
-        <v>0.163</v>
+        <v>0.254</v>
       </c>
       <c r="E3">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="F3">
-        <v>22.345</v>
+        <v>38.732</v>
       </c>
       <c r="G3">
-        <v>22.982</v>
+        <v>39.728</v>
       </c>
       <c r="H3">
-        <v>22.331</v>
+        <v>38.783</v>
       </c>
       <c r="I3">
-        <v>22.971</v>
+        <v>39.755</v>
       </c>
       <c r="J3">
-        <v>22.352</v>
+        <v>38.725</v>
       </c>
       <c r="K3">
-        <v>22.991</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>39.36</v>
-      </c>
-      <c r="C4">
-        <v>0.057</v>
-      </c>
-      <c r="D4">
-        <v>0.24</v>
-      </c>
-      <c r="E4">
-        <v>0.008</v>
-      </c>
-      <c r="F4">
-        <v>38.897</v>
-      </c>
-      <c r="G4">
-        <v>39.837</v>
-      </c>
-      <c r="H4">
-        <v>38.874</v>
-      </c>
-      <c r="I4">
-        <v>39.822</v>
-      </c>
-      <c r="J4">
-        <v>38.906</v>
-      </c>
-      <c r="K4">
-        <v>39.854</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>23.355</v>
-      </c>
-      <c r="C5">
-        <v>0.026</v>
-      </c>
-      <c r="D5">
-        <v>0.16</v>
-      </c>
-      <c r="E5">
-        <v>0.005</v>
-      </c>
-      <c r="F5">
-        <v>23.044</v>
-      </c>
-      <c r="G5">
-        <v>23.673</v>
-      </c>
-      <c r="H5">
-        <v>23.038</v>
-      </c>
-      <c r="I5">
-        <v>23.654</v>
-      </c>
-      <c r="J5">
-        <v>23.06</v>
-      </c>
-      <c r="K5">
-        <v>23.676</v>
+        <v>39.697</v>
       </c>
     </row>
   </sheetData>
